--- a/utils/monday_sprint_sprint_2026-08.xlsx
+++ b/utils/monday_sprint_sprint_2026-08.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="253">
   <si>
     <t>Ticket</t>
   </si>
@@ -117,7 +117,7 @@
     <t>15/10/2024</t>
   </si>
   <si>
-    <t>29/03/2026</t>
+    <t>24/03/2026</t>
   </si>
   <si>
     <t>Semana 3</t>
@@ -162,7 +162,7 @@
     <t>25/09/2025</t>
   </si>
   <si>
-    <t>15/04/2026</t>
+    <t>10/04/2026</t>
   </si>
   <si>
     <t>Homologação</t>
@@ -237,9 +237,6 @@
     <t>27/11/2025</t>
   </si>
   <si>
-    <t>10/04/2026</t>
-  </si>
-  <si>
     <t>Novembro</t>
   </si>
   <si>
@@ -249,445 +246,409 @@
     <t>Add opção de revisão valor de frete na CPC</t>
   </si>
   <si>
-    <t>@Maciel, bom dia! Conforme conversamos, por gentileza adicionar uma tela para revisão de tipo de frete na CPC. Precisamos ter qual a nova opção de frete (DAP, DDP, FOB, etc.) e qual o valor da diferença. Obrigada!</t>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>25173</t>
+  </si>
+  <si>
+    <t>Peças Faturadas</t>
+  </si>
+  <si>
+    <t>Boa tarde Srs., Preciso que seja desenvolvido no QlikSense uma tabela trazendo todos os modelos faturados por mês / ano e seus devidos valores cobrados (FTF) para ensaios de qualidade. Descrição (Códigos FTF): · Hidrostático (7242); · Dimensional Braço Faro (7250) · Fotogrametria (7268); · Dimension</t>
+  </si>
+  <si>
+    <t>18/03/2024</t>
+  </si>
+  <si>
+    <t>Março</t>
+  </si>
+  <si>
+    <t>36780</t>
+  </si>
+  <si>
+    <t>Acessos anônimos</t>
+  </si>
+  <si>
+    <t>Prezados, Precisamos bloquear os acessos anônimos no sistema, mesmo que para consulta. Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Edson João Hammermeister</t>
+  </si>
+  <si>
+    <t>20/02/2026</t>
+  </si>
+  <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>36046</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Aprimoramento Ailton - Valorização de modelos</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Criar agendamento que dispare o envio do lote de produtos.</t>
   </si>
   <si>
     <t>Laura Herrmann Schmickler</t>
   </si>
   <si>
+    <t>28/07/2025</t>
+  </si>
+  <si>
+    <t>36320</t>
+  </si>
+  <si>
+    <t>Linkar gatilho de ACR com TV manutenções (Central + Usinagem)</t>
+  </si>
+  <si>
+    <t>Bom dia, Estou solicitando que façamos um link entre os gatilhos de ACR e a gestão visual nas TVs. A ideia é implementar gestão visual além da tarja amarela, sinalizando visualmente quando algum dos gatilhos forem atingidos (Tempo e frequencia) Att,</t>
+  </si>
+  <si>
+    <t>Enzo Luiz Okabe Auad</t>
+  </si>
+  <si>
+    <t>29/01/2026</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>36556</t>
+  </si>
+  <si>
+    <t>Correção</t>
+  </si>
+  <si>
+    <t>Problema</t>
+  </si>
+  <si>
+    <t>B.I. Acabamento - Reunião</t>
+  </si>
+  <si>
+    <t>Boa tarde Srs., Identifiquei mais um erro no B.I., onde um mesmo apontamento para 3 pe?as diferentes, est? sendo replicado, ao inv?s de ratear o tempo entre elas. Veja abaixo, o apontamento inicia as 23:15 e finaliza as 23:35 (20 min), deveria ser contabilizado 00:06:40 para cada pe?a: Filtros usado</t>
+  </si>
+  <si>
+    <t>09/02/2026</t>
+  </si>
+  <si>
+    <t>36626</t>
+  </si>
+  <si>
+    <t>Incremento ao BI "Peso por área" - Extração do Histórico do MPS</t>
+  </si>
+  <si>
+    <t>Bom dia, Felipe. Conforme falamos por ligação, preciso que seja realizado um incremento no BI de "Peso por área" para que seja possível visualizarmos o peso histórico filtrado por setor, e não apenas por grupo de etapa que é o caso atual. Anexo uma imagem do estado atual, neste gráfico eu gostaria s</t>
+  </si>
+  <si>
+    <t>Lucas da Silva Machado</t>
+  </si>
+  <si>
+    <t>11235596736</t>
+  </si>
+  <si>
+    <t>Conversão KB Manutenção -  Crud</t>
+  </si>
+  <si>
+    <t>Ajustar as oportunidades já enviadas com a fase da oportunidade.</t>
+  </si>
+  <si>
+    <t>B.I. Acabamento</t>
+  </si>
+  <si>
+    <t>31977</t>
+  </si>
+  <si>
+    <t>Alterações no registro de moldagem via APP - Validação</t>
+  </si>
+  <si>
+    <t>36730</t>
+  </si>
+  <si>
+    <t>Arvore de Ativos no sistema SMI</t>
+  </si>
+  <si>
+    <t>Olá, Necessitamos que seja incluído a arvore de ativos no sistema de manutenção de forma massiva. Temos documentos em excel com as informações necessárias para a inclusão. Att,</t>
+  </si>
+  <si>
+    <t>Luiz Henrique Rocha Junior</t>
+  </si>
+  <si>
+    <t>18/02/2026</t>
+  </si>
+  <si>
+    <t>18/03/2026</t>
+  </si>
+  <si>
+    <t>23838</t>
+  </si>
+  <si>
+    <t>Novo Sistema</t>
+  </si>
+  <si>
+    <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema (copy)</t>
+  </si>
+  <si>
+    <t>35792</t>
+  </si>
+  <si>
+    <t>Criação de campos no sistema de manutenção</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, Precisamos criar alguns campos na janela de requisições do almoxarifado no sistema manutenção, a finalidade é que conseguimos ter informações precisas referentes ao material requisitado. Os campos seriam: Família/Máquina/Código/Marca. Em anexo estou enviando uma imagem de sugestão, estou a </t>
+  </si>
+  <si>
+    <t>Vitor de Oliveira da Silva</t>
+  </si>
+  <si>
+    <t>18/12/2025</t>
+  </si>
+  <si>
+    <t>Dezembro</t>
+  </si>
+  <si>
+    <t>Criar procedimento que envie lotes de produtos cadastrados.</t>
+  </si>
+  <si>
+    <t>36213</t>
+  </si>
+  <si>
+    <t>Alteração no sistema de manutenção</t>
+  </si>
+  <si>
+    <t>Bom dia, Estamos solicitando que seja feito uma alteração no sistema de manutenção que envolve a seguinte mudança: Ordens preventivas e provenientes de métodos não devem ser programadas diretas, devem passar pela programação antes, ou seja, devem ser abertas com status de aguardando programação. Con</t>
+  </si>
+  <si>
+    <t>34073</t>
+  </si>
+  <si>
+    <t>ALTC - Adicionar botão para visualização da FTFU (CPP123,CPP39)</t>
+  </si>
+  <si>
+    <t>36232</t>
+  </si>
+  <si>
+    <t>Report técnico</t>
+  </si>
+  <si>
+    <t>Boa tarde, Solicito um chamado para automatizar a tabela de report técnico, em anexo, no e-mail. Esses dados são retirados do nosso sistema de manutenção e está apto a melhoria. Se possível, com as informações gerar um Dashboard. A ideia seria analisar mais dados com um número maior de ordens por ma</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>36724</t>
+  </si>
+  <si>
+    <t>Alteração de registro de pintura</t>
+  </si>
+  <si>
+    <t>36526</t>
+  </si>
+  <si>
+    <t>Tempo de parada Carrossel</t>
+  </si>
+  <si>
+    <t>23773</t>
+  </si>
+  <si>
+    <t>Registro de moldagem USE/ULE</t>
+  </si>
+  <si>
+    <t>Bom dia, Estamos tendo inconsistência nos registros de Moldagem USE/ULE, acontece às vezes do registro ser finalizado e a movimentação não ocorrer. Ocorre tanto na ULE como na USE. Exemplos abaixo: Duvidas entrar em contato. Att.</t>
+  </si>
+  <si>
+    <t>Darlan Pressi</t>
+  </si>
+  <si>
+    <t>19/12/2023</t>
+  </si>
+  <si>
+    <t>22/04/2026</t>
+  </si>
+  <si>
+    <t>36493</t>
+  </si>
+  <si>
+    <t>Apontamento Eletrônico Acabamento - Analise</t>
+  </si>
+  <si>
+    <t>36722</t>
+  </si>
+  <si>
+    <t>Bloco K - Integração dados Altona / Benner.</t>
+  </si>
+  <si>
+    <t>35738</t>
+  </si>
+  <si>
+    <t>Melhoria apontamento de corte de canais - Reunião</t>
+  </si>
+  <si>
+    <t>Bom dia, Melhoria no apontamento de peças do sistema de corte de canais eletrônico, talvez criar um campo de pergunta se o cortador vai cortar 1 peça ou uma penca, se for penca abrir uma lista onde ele possa inserir todas as sequência de uma vez sem ter que ficar digitando todas as informações em ca</t>
+  </si>
+  <si>
+    <t>Eduardo Basso Pinto</t>
+  </si>
+  <si>
+    <t>16/12/2025</t>
+  </si>
+  <si>
+    <t>ALTC - Adicionar consulta de ensaios realizados F9</t>
+  </si>
+  <si>
+    <t>35081</t>
+  </si>
+  <si>
+    <t>SUGESTÃO PARA MELHORIA NA H5000 - Reunião</t>
+  </si>
+  <si>
+    <t>Bom dia, tudo certo? Gostaria de fazer uma sugestão de melhoria na H5000 com relação ao preenchimento da carta CEP e C3M. * Atualmente 1° - Atualmente o preenchimento desses dois arquivos são feitos manualmente, imprimimos o arquivo de excell para o operador e ele faz o preenchimento de forma manual</t>
+  </si>
+  <si>
+    <t>Wangadner Maycoll do Nascimento Costa</t>
+  </si>
+  <si>
+    <t>04/11/2025</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>31699</t>
+  </si>
+  <si>
+    <t>Cadastro de TOKEN Ailton</t>
+  </si>
+  <si>
+    <t>19909</t>
+  </si>
+  <si>
+    <t>Criar KB Genexus especifica para Registro de pinturas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, Visando uma melhoria no setor de pintura e uma adequação para ISO9001, o registro de pintura é hoje realizado manualmente pelo pintor, correndo assim, o risco do mesmo esquecer de preencher o documento ao final da atividade. A ideia seria inserir um registro digital, parecido com o que é </t>
+  </si>
+  <si>
+    <t>Caio Henrique Vicente Bento</t>
+  </si>
+  <si>
+    <t>25/04/2023</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>34225</t>
+  </si>
+  <si>
+    <t>Correções Relatório Fatuamento por Sequência</t>
+  </si>
+  <si>
+    <t>Sandro, bom dia! Solicito melhorias a seguir no Relatório Faturamento por Sequência. * Desconsiderar NF que não se tratam de venda (receita), por exemplo 210982/212675/213384/213385 (CFOP 5.949./6.949/7.949 - Remessa Conserto e Outros) NFe 213069 valor incorreto retornado no relatório.</t>
+  </si>
+  <si>
+    <t>19/09/2025</t>
+  </si>
+  <si>
+    <t>36349</t>
+  </si>
+  <si>
+    <t>Erro ao excluir planos de ação - Gestão de ações</t>
+  </si>
+  <si>
+    <t>36705</t>
+  </si>
+  <si>
+    <t>MODIFICAÇÃO NO SISTEMA DE MANUTENÇÃO</t>
+  </si>
+  <si>
+    <t>Boa tarde, Gostaria de adicionar uma opção no sistema de manutenção, na aba de "permissões" - Adicionar um limite de ordens em andamento, como o exemplo abaixo: (além do "Limite de Paradas Permitidas", colocar o "Limite de ordens em andamento"). Aguardo retorno,</t>
+  </si>
+  <si>
+    <t>Guilherme Ferreira</t>
+  </si>
+  <si>
+    <t>36210</t>
+  </si>
+  <si>
+    <t>[Residência em IA] Altona 1 - Envio de Resultados - Sprint 2</t>
+  </si>
+  <si>
+    <t>36206</t>
+  </si>
+  <si>
+    <t>Cadastro de LEADs para Desenvolvimento de Negócios - API</t>
+  </si>
+  <si>
+    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
+  </si>
+  <si>
+    <t>Adnan Pires</t>
+  </si>
+  <si>
+    <t>22/01/2026</t>
+  </si>
+  <si>
+    <t>36484</t>
+  </si>
+  <si>
+    <t>Melhoria da Tela de Tickets</t>
+  </si>
+  <si>
+    <t>Bom dia Maciel, Conforme falamos, precisamos melhorar a tela para a seleção das sequencias nos tickets, para reduzir o tempo de emissão das etiquetas. Alterando as telas abaixo, para que possamos abrir uma única vez a tela e selecionar a sequência e o ticket a ser incluído, passando para o próximo a</t>
+  </si>
+  <si>
+    <t>Vanessa Karsten</t>
+  </si>
+  <si>
+    <t>05/02/2026</t>
+  </si>
+  <si>
+    <t>36338</t>
+  </si>
+  <si>
+    <t>Listagem de CPCs do cliente Minera San Cristóbal com a margem de Contribuição</t>
+  </si>
+  <si>
+    <t>Boa tarde Maciel, Gentileza enviar uma lista das CPCs feitas para o cliente Minera San Cristóbal (código 21189), referente aos anos de 2024 e 2025 com suas respectivas margens de contribuição. Precisamos com urgência desse relatório para solicitação da diretoria comercial. Att.</t>
+  </si>
+  <si>
+    <t>Jaqueline Cogorni Mendes</t>
+  </si>
+  <si>
+    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
+  </si>
+  <si>
+    <t>36778</t>
+  </si>
+  <si>
+    <t>Revogação de acessos - Troca de área</t>
+  </si>
+  <si>
+    <t>Ajustar o envio de oportunidade para levar a fase que a oportunidade está (funil de vendas).</t>
+  </si>
+  <si>
+    <t>Criar procedimento que envie lotes de Oportunidades</t>
+  </si>
+  <si>
+    <t>36407</t>
+  </si>
+  <si>
+    <t>Tela para programação de moldagem</t>
+  </si>
+  <si>
+    <t>Boa tarde, Precisamos desenvolver uma tela no sistema para auxiliar a programação das moldagens. Este processo atualmente é feito de maneira manual em planilhas de excel. Anexo está inserida uma planilha com as informações que precisamos nesta tela, a ideia é de que o programados informe a sequência</t>
+  </si>
+  <si>
     <t>02/02/2026</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>25173</t>
-  </si>
-  <si>
-    <t>Peças Faturadas</t>
-  </si>
-  <si>
-    <t>Boa tarde Srs., Preciso que seja desenvolvido no QlikSense uma tabela trazendo todos os modelos faturados por mês / ano e seus devidos valores cobrados (FTF) para ensaios de qualidade. Descrição (Códigos FTF): · Hidrostático (7242); · Dimensional Braço Faro (7250) · Fotogrametria (7268); · Dimension</t>
-  </si>
-  <si>
-    <t>18/03/2024</t>
-  </si>
-  <si>
-    <t>Março</t>
-  </si>
-  <si>
-    <t>36780</t>
-  </si>
-  <si>
-    <t>Acessos anônimos</t>
-  </si>
-  <si>
-    <t>Prezados, Precisamos bloquear os acessos anônimos no sistema, mesmo que para consulta. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Edson João Hammermeister</t>
-  </si>
-  <si>
-    <t>20/02/2026</t>
-  </si>
-  <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>36046</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Aprimoramento Ailton - Valorização de modelos</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Criar agendamento que dispare o envio do lote de produtos.</t>
-  </si>
-  <si>
-    <t>28/07/2025</t>
-  </si>
-  <si>
-    <t>36320</t>
-  </si>
-  <si>
-    <t>Linkar gatilho de ACR com TV manutenções (Central + Usinagem)</t>
-  </si>
-  <si>
-    <t>Bom dia, Estou solicitando que façamos um link entre os gatilhos de ACR e a gestão visual nas TVs. A ideia é implementar gestão visual além da tarja amarela, sinalizando visualmente quando algum dos gatilhos forem atingidos (Tempo e frequencia) Att,</t>
-  </si>
-  <si>
-    <t>Enzo Luiz Okabe Auad</t>
-  </si>
-  <si>
-    <t>29/01/2026</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
-  </si>
-  <si>
-    <t>36556</t>
-  </si>
-  <si>
-    <t>Correção</t>
-  </si>
-  <si>
-    <t>Problema</t>
-  </si>
-  <si>
-    <t>B.I. Acabamento - Reunião</t>
-  </si>
-  <si>
-    <t>Boa tarde Srs., Identifiquei mais um erro no B.I., onde um mesmo apontamento para 3 pe?as diferentes, est? sendo replicado, ao inv?s de ratear o tempo entre elas. Veja abaixo, o apontamento inicia as 23:15 e finaliza as 23:35 (20 min), deveria ser contabilizado 00:06:40 para cada pe?a: Filtros usado</t>
-  </si>
-  <si>
-    <t>09/02/2026</t>
-  </si>
-  <si>
-    <t>36626</t>
-  </si>
-  <si>
-    <t>Incremento ao BI "Peso por área" - Extração do Histórico do MPS</t>
-  </si>
-  <si>
-    <t>Bom dia, Felipe. Conforme falamos por ligação, preciso que seja realizado um incremento no BI de "Peso por área" para que seja possível visualizarmos o peso histórico filtrado por setor, e não apenas por grupo de etapa que é o caso atual. Anexo uma imagem do estado atual, neste gráfico eu gostaria s</t>
-  </si>
-  <si>
-    <t>Lucas da Silva Machado</t>
-  </si>
-  <si>
-    <t>11235596736</t>
-  </si>
-  <si>
-    <t>Conversão KB Manutenção -  Crud</t>
-  </si>
-  <si>
-    <t>Ajustar as oportunidades já enviadas com a fase da oportunidade.</t>
-  </si>
-  <si>
-    <t>B.I. Acabamento</t>
-  </si>
-  <si>
-    <t>31977</t>
-  </si>
-  <si>
-    <t>Alterações no registro de moldagem via APP - Validação</t>
-  </si>
-  <si>
-    <t>36730</t>
-  </si>
-  <si>
-    <t>Arvore de Ativos no sistema SMI</t>
-  </si>
-  <si>
-    <t>Olá, Necessitamos que seja incluído a arvore de ativos no sistema de manutenção de forma massiva. Temos documentos em excel com as informações necessárias para a inclusão. Att,</t>
-  </si>
-  <si>
-    <t>Luiz Henrique Rocha Junior</t>
-  </si>
-  <si>
-    <t>18/02/2026</t>
-  </si>
-  <si>
-    <t>23/03/2026</t>
-  </si>
-  <si>
-    <t>23838</t>
-  </si>
-  <si>
-    <t>Novo Sistema</t>
-  </si>
-  <si>
-    <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema (copy)</t>
-  </si>
-  <si>
-    <t>35792</t>
-  </si>
-  <si>
-    <t>Criação de campos no sistema de manutenção</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, Precisamos criar alguns campos na janela de requisições do almoxarifado no sistema manutenção, a finalidade é que conseguimos ter informações precisas referentes ao material requisitado. Os campos seriam: Família/Máquina/Código/Marca. Em anexo estou enviando uma imagem de sugestão, estou a </t>
-  </si>
-  <si>
-    <t>Vitor de Oliveira da Silva</t>
-  </si>
-  <si>
-    <t>18/12/2025</t>
-  </si>
-  <si>
-    <t>Dezembro</t>
-  </si>
-  <si>
-    <t>Criar procedimento que envie lotes de produtos cadastrados.</t>
-  </si>
-  <si>
-    <t>36213</t>
-  </si>
-  <si>
-    <t>Alteração no sistema de manutenção</t>
-  </si>
-  <si>
-    <t>Bom dia, Estamos solicitando que seja feito uma alteração no sistema de manutenção que envolve a seguinte mudança: Ordens preventivas e provenientes de métodos não devem ser programadas diretas, devem passar pela programação antes, ou seja, devem ser abertas com status de aguardando programação. Con</t>
-  </si>
-  <si>
-    <t>34073</t>
-  </si>
-  <si>
-    <t>ALTC - Adicionar botão para visualização da FTFU (CPP123,CPP39)</t>
-  </si>
-  <si>
-    <t>36232</t>
-  </si>
-  <si>
-    <t>Report técnico</t>
-  </si>
-  <si>
-    <t>36724</t>
-  </si>
-  <si>
-    <t>Alteração de registro de pintura</t>
-  </si>
-  <si>
-    <t>Sistema de registro de pintura: Teria como o Log aparecer de uma forma parecida com essa descrição? ( Cadastro de quem alterou), (Descrição do que foi alterado Ex. Alterado medição da camada Top Coat com tolerância: Min.: ........., Max.: .........., Medição anterior: ............, Alterado para: ..</t>
-  </si>
-  <si>
-    <t>Lucas Sebold Movidesk</t>
-  </si>
-  <si>
-    <t>36526</t>
-  </si>
-  <si>
-    <t>Tempo de parada Carrossel</t>
-  </si>
-  <si>
-    <t>Verificar ao retomar o apontamento o tempo de parada está como 1seg, mesmo tendo parado por mais de 10min</t>
-  </si>
-  <si>
-    <t>06/02/2026</t>
-  </si>
-  <si>
-    <t>23773</t>
-  </si>
-  <si>
-    <t>Registro de moldagem USE/ULE</t>
-  </si>
-  <si>
-    <t>Bom dia, Estamos tendo inconsistência nos registros de Moldagem USE/ULE, acontece às vezes do registro ser finalizado e a movimentação não ocorrer. Ocorre tanto na ULE como na USE. Exemplos abaixo: Duvidas entrar em contato. Att.</t>
-  </si>
-  <si>
-    <t>Darlan Pressi</t>
-  </si>
-  <si>
-    <t>19/12/2023</t>
-  </si>
-  <si>
-    <t>27/04/2026</t>
-  </si>
-  <si>
-    <t>36493</t>
-  </si>
-  <si>
-    <t>Apontamento Eletrônico Acabamento - Analise</t>
-  </si>
-  <si>
-    <t>Bom dia Luiz, por gentileza verificar a possibilidade de instalar o Apontamento eletrônico Acabamento nos tabletes que os soldadores estão usando, intuito disso é para os soldadores ganhar tempo ao fazer seus apontamentos dentro das cabines de solda sem a necessidade de deslocar até um PC na produçã</t>
-  </si>
-  <si>
-    <t>Danilo da Silva Pereira</t>
-  </si>
-  <si>
-    <t>05/02/2026</t>
-  </si>
-  <si>
-    <t>36722</t>
-  </si>
-  <si>
-    <t>Bloco K - Integração dados Altona / Benner.</t>
-  </si>
-  <si>
-    <t>Prezado, bom dia. Situação: Atualmente a integração dos dados Altona / Benner, para integrar o bloco K, precisa da intervenção de uma pessoa para disparar a rotina. Necessidade: Automatizar este processo. Ação: 1. Implementar status indicando que o dado está pronto para ser enviado para Benner. 2. A</t>
-  </si>
-  <si>
-    <t>Alexandre Longo</t>
-  </si>
-  <si>
-    <t>35738</t>
-  </si>
-  <si>
-    <t>Melhoria apontamento de corte de canais - Reunião</t>
-  </si>
-  <si>
-    <t>Bom dia, Melhoria no apontamento de peças do sistema de corte de canais eletrônico, talvez criar um campo de pergunta se o cortador vai cortar 1 peça ou uma penca, se for penca abrir uma lista onde ele possa inserir todas as sequência de uma vez sem ter que ficar digitando todas as informações em ca</t>
-  </si>
-  <si>
-    <t>Eduardo Basso Pinto</t>
-  </si>
-  <si>
-    <t>16/12/2025</t>
-  </si>
-  <si>
-    <t>ALTC - Adicionar consulta de ensaios realizados F9</t>
-  </si>
-  <si>
-    <t>35081</t>
-  </si>
-  <si>
-    <t>SUGESTÃO PARA MELHORIA NA H5000 - Reunião</t>
-  </si>
-  <si>
-    <t>Bom dia, tudo certo? Gostaria de fazer uma sugestão de melhoria na H5000 com relação ao preenchimento da carta CEP e C3M. * Atualmente 1° - Atualmente o preenchimento desses dois arquivos são feitos manualmente, imprimimos o arquivo de excell para o operador e ele faz o preenchimento de forma manual</t>
-  </si>
-  <si>
-    <t>Wangadner Maycoll do Nascimento Costa</t>
-  </si>
-  <si>
-    <t>04/11/2025</t>
-  </si>
-  <si>
-    <t>31699</t>
-  </si>
-  <si>
-    <t>Cadastro de TOKEN Ailton</t>
-  </si>
-  <si>
-    <t>19909</t>
-  </si>
-  <si>
-    <t>Criar KB Genexus especifica para Registro de pinturas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, Visando uma melhoria no setor de pintura e uma adequação para ISO9001, o registro de pintura é hoje realizado manualmente pelo pintor, correndo assim, o risco do mesmo esquecer de preencher o documento ao final da atividade. A ideia seria inserir um registro digital, parecido com o que é </t>
-  </si>
-  <si>
-    <t>Caio Henrique Vicente Bento</t>
-  </si>
-  <si>
-    <t>25/04/2023</t>
-  </si>
-  <si>
-    <t>23/02/2026</t>
-  </si>
-  <si>
-    <t>Abril</t>
-  </si>
-  <si>
-    <t>34225</t>
-  </si>
-  <si>
-    <t>Correções Relatório Fatuamento por Sequência</t>
-  </si>
-  <si>
-    <t>Sandro, bom dia! Solicito melhorias a seguir no Relatório Faturamento por Sequência. * Desconsiderar NF que não se tratam de venda (receita), por exemplo 210982/212675/213384/213385 (CFOP 5.949./6.949/7.949 - Remessa Conserto e Outros) NFe 213069 valor incorreto retornado no relatório.</t>
-  </si>
-  <si>
-    <t>19/09/2025</t>
-  </si>
-  <si>
-    <t>36349</t>
-  </si>
-  <si>
-    <t>Erro ao excluir planos de ação - Gestão de ações</t>
-  </si>
-  <si>
-    <t>Boa tarde pessoal, Ao tentar excluir planos de ação o sistema Gestão de Ações, sou direcionado para uma nova aba de "erro". Por gentileza, vocês podem verificar? 1- 2- Atenciosamente;</t>
-  </si>
-  <si>
-    <t>Matheus Gonçalves</t>
-  </si>
-  <si>
-    <t>36705</t>
-  </si>
-  <si>
-    <t>MODIFICAÇÃO NO SISTEMA DE MANUTENÇÃO</t>
-  </si>
-  <si>
-    <t>Boa tarde, Gostaria de adicionar uma opção no sistema de manutenção, na aba de "permissões" - Adicionar um limite de ordens em andamento, como o exemplo abaixo: (além do "Limite de Paradas Permitidas", colocar o "Limite de ordens em andamento"). Aguardo retorno,</t>
-  </si>
-  <si>
-    <t>Guilherme Ferreira</t>
-  </si>
-  <si>
-    <t>36210</t>
-  </si>
-  <si>
-    <t>[Residência em IA] Altona 1 - Envio de Resultados - Sprint 2</t>
-  </si>
-  <si>
-    <t>De: JUAN PABLO CHAVARRO SANCHEZ Enviada em: quarta-feira, 21 de janeiro de 2026 12:40 Para: Edson João Hammermeister ; Fernanda da Costa Rodrigues ; Flavio Bett ; Gilsimar Carls ; João Pedro Beccon ; Mauro Morais ; Samuel Garcia ; Taynara Frare Assunto: [Residência em IA] Altona 1 - Envio de Resulta</t>
-  </si>
-  <si>
-    <t>22/01/2026</t>
-  </si>
-  <si>
-    <t>36206</t>
-  </si>
-  <si>
-    <t>Cadastro de LEADs para Desenvolvimento de Negócios - API</t>
-  </si>
-  <si>
-    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
-  </si>
-  <si>
-    <t>Adnan Pires</t>
-  </si>
-  <si>
-    <t>36484</t>
-  </si>
-  <si>
-    <t>Melhoria da Tela de Tickets</t>
-  </si>
-  <si>
-    <t>Bom dia Maciel, Conforme falamos, precisamos melhorar a tela para a seleção das sequencias nos tickets, para reduzir o tempo de emissão das etiquetas. Alterando as telas abaixo, para que possamos abrir uma única vez a tela e selecionar a sequência e o ticket a ser incluído, passando para o próximo a</t>
-  </si>
-  <si>
-    <t>Vanessa Karsten</t>
-  </si>
-  <si>
-    <t>36338</t>
-  </si>
-  <si>
-    <t>Listagem de CPCs do cliente Minera San Cristóbal com a margem de Contribuição</t>
-  </si>
-  <si>
-    <t>Boa tarde Maciel, Gentileza enviar uma lista das CPCs feitas para o cliente Minera San Cristóbal (código 21189), referente aos anos de 2024 e 2025 com suas respectivas margens de contribuição. Precisamos com urgência desse relatório para solicitação da diretoria comercial. Att.</t>
-  </si>
-  <si>
-    <t>Jaqueline Cogorni Mendes</t>
-  </si>
-  <si>
-    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
-  </si>
-  <si>
-    <t>36778</t>
-  </si>
-  <si>
-    <t>Revogação de acessos - Troca de área</t>
-  </si>
-  <si>
-    <t>Prezados, Precisamos desenvolver um processo para revogar os acessos do usuário ao trocar de área no DHO. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Ajustar o envio de oportunidade para levar a fase que a oportunidade está (funil de vendas).</t>
-  </si>
-  <si>
-    <t>Criar procedimento que envie lotes de Oportunidades</t>
-  </si>
-  <si>
-    <t>36407</t>
-  </si>
-  <si>
-    <t>Tela para programação de moldagem</t>
-  </si>
-  <si>
-    <t>Boa tarde, Precisamos desenvolver uma tela no sistema para auxiliar a programação das moldagens. Este processo atualmente é feito de maneira manual em planilhas de excel. Anexo está inserida uma planilha com as informações que precisamos nesta tela, a ideia é de que o programados informe a sequência</t>
   </si>
   <si>
     <t>36467</t>
@@ -1671,7 +1632,7 @@
         <v>73</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1680,12 +1641,12 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
@@ -1694,42 +1655,42 @@
         <v>16</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>15</v>
@@ -1741,10 +1702,10 @@
         <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1756,7 +1717,7 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>34</v>
@@ -1768,12 +1729,12 @@
         <v>35</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
@@ -1785,28 +1746,28 @@
         <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>35</v>
@@ -1817,22 +1778,22 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1861,7 +1822,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -1873,7 +1834,7 @@
         <v>17</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>24</v>
@@ -1882,19 +1843,19 @@
         <v>20</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>26</v>
@@ -1905,7 +1866,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>15</v>
@@ -1917,31 +1878,31 @@
         <v>17</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>49</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>58</v>
@@ -1949,22 +1910,22 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>55</v>
@@ -1976,7 +1937,7 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>34</v>
@@ -1993,7 +1954,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
@@ -2005,16 +1966,16 @@
         <v>17</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>22</v>
@@ -2037,7 +1998,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
@@ -2049,10 +2010,10 @@
         <v>24</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>55</v>
@@ -2070,7 +2031,7 @@
         <v>24</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>43</v>
@@ -2081,7 +2042,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
@@ -2093,7 +2054,7 @@
         <v>17</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>24</v>
@@ -2102,19 +2063,19 @@
         <v>20</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>26</v>
@@ -2125,22 +2086,22 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -2152,7 +2113,7 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>34</v>
@@ -2169,7 +2130,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -2181,10 +2142,10 @@
         <v>24</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2213,7 +2174,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -2225,25 +2186,25 @@
         <v>17</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>66</v>
@@ -2257,22 +2218,22 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>55</v>
@@ -2290,7 +2251,7 @@
         <v>24</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>26</v>
@@ -2301,7 +2262,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -2313,39 +2274,39 @@
         <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>34</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>35</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2357,7 +2318,7 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>24</v>
@@ -2366,13 +2327,13 @@
         <v>20</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>24</v>
@@ -2389,7 +2350,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -2401,16 +2362,16 @@
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>22</v>
@@ -2433,22 +2394,22 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>55</v>
@@ -2477,7 +2438,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -2486,28 +2447,28 @@
         <v>16</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2516,12 +2477,12 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2530,42 +2491,42 @@
         <v>16</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>148</v>
+        <v>24</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>35</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -2574,86 +2535,86 @@
         <v>16</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>35</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
@@ -2662,25 +2623,25 @@
         <v>16</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>162</v>
+        <v>24</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>163</v>
+        <v>24</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>24</v>
@@ -2689,15 +2650,15 @@
         <v>25</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -2706,42 +2667,42 @@
         <v>16</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>167</v>
+        <v>24</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>35</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -2753,22 +2714,22 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>49</v>
@@ -2780,27 +2741,27 @@
         <v>35</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>55</v>
@@ -2829,7 +2790,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -2841,54 +2802,54 @@
         <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2917,7 +2878,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -2929,25 +2890,25 @@
         <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>186</v>
+        <v>122</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>50</v>
@@ -2956,12 +2917,12 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -2973,10 +2934,10 @@
         <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>55</v>
@@ -2988,10 +2949,10 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -3005,51 +2966,51 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>195</v>
+        <v>24</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -3061,16 +3022,16 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>22</v>
@@ -3082,7 +3043,7 @@
         <v>34</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>35</v>
@@ -3093,84 +3054,84 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>203</v>
+        <v>24</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M44" s="2" t="s">
         <v>26</v>
@@ -3181,7 +3142,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
@@ -3193,22 +3154,22 @@
         <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>34</v>
@@ -3217,7 +3178,7 @@
         <v>42</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>44</v>
@@ -3225,34 +3186,34 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>34</v>
@@ -3261,7 +3222,7 @@
         <v>50</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>58</v>
@@ -3269,40 +3230,40 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M47" s="2" t="s">
         <v>26</v>
@@ -3313,7 +3274,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3322,42 +3283,42 @@
         <v>16</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M48" s="2" t="s">
         <v>35</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3369,7 +3330,7 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>24</v>
@@ -3378,13 +3339,13 @@
         <v>20</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>24</v>
@@ -3401,7 +3362,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3413,7 +3374,7 @@
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>24</v>
@@ -3422,19 +3383,19 @@
         <v>20</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>26</v>
@@ -3445,7 +3406,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3457,22 +3418,22 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>24</v>
@@ -3481,7 +3442,7 @@
         <v>42</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>44</v>
@@ -3489,43 +3450,43 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>49</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>44</v>
@@ -3533,7 +3494,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3545,28 +3506,28 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>49</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>35</v>
@@ -3577,7 +3538,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3589,7 +3550,7 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>24</v>
@@ -3598,13 +3559,13 @@
         <v>55</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>24</v>
@@ -3621,22 +3582,22 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>55</v>
@@ -3654,7 +3615,7 @@
         <v>24</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M55" s="2" t="s">
         <v>26</v>
@@ -3665,7 +3626,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3677,10 +3638,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3720,23 +3681,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="D2" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="E2" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3744,16 +3705,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3772,7 +3733,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3793,7 +3754,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3824,12 +3785,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="B2">
         <v>55</v>
@@ -3853,25 +3814,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3888,13 +3849,13 @@
         <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3906,15 +3867,15 @@
         <v>22</v>
       </c>
       <c r="P10" t="s">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E11">
         <v>7</v>
@@ -3926,13 +3887,13 @@
         <v>24</v>
       </c>
       <c r="J11" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="K11">
         <v>55</v>
       </c>
       <c r="M11" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="N11">
         <v>17</v>
@@ -3941,12 +3902,12 @@
         <v>43</v>
       </c>
       <c r="Q11">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -3967,24 +3928,24 @@
         <v>35</v>
       </c>
       <c r="Q12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="N13">
         <v>6</v>
@@ -3993,12 +3954,12 @@
         <v>26</v>
       </c>
       <c r="Q13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -4008,12 +3969,6 @@
       </c>
       <c r="N14">
         <v>4</v>
-      </c>
-      <c r="P14" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q14">
-        <v>6</v>
       </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
@@ -4026,7 +3981,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4034,7 +3989,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4042,7 +3997,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -4053,7 +4008,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -4061,44 +4016,44 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4109,7 +4064,7 @@
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>29</v>
@@ -4123,7 +4078,7 @@
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>18</v>
@@ -4131,72 +4086,72 @@
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2026-08.xlsx
+++ b/utils/monday_sprint_sprint_2026-08.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="247">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -90,198 +90,216 @@
     <t>20/02/2026</t>
   </si>
   <si>
+    <t>08/03/2026</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>Fevereiro</t>
+  </si>
+  <si>
+    <t>28392</t>
+  </si>
+  <si>
+    <t>Contabilidade</t>
+  </si>
+  <si>
+    <t>Notas de consignado - Medição NIMBI</t>
+  </si>
+  <si>
+    <t>Bom dia, Conforme reunião dia 10/10 com o Sandro, queremos solicitar uma alteração no sistema de consignados da empresa. Sobre os contratos de consignado será gerado uma ordem de compra, e dentro dessas ordens terão medições para os consumos dos consignados. Para verificar que a OC é referente a con</t>
+  </si>
+  <si>
+    <t>Jessica Priscila Gonçalves</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>23/02/2026</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>11344688924</t>
+  </si>
+  <si>
+    <t>Setor não informado</t>
+  </si>
+  <si>
+    <t>Categoria não informada</t>
+  </si>
+  <si>
+    <t>Multiplos de Caixa de ferro</t>
+  </si>
+  <si>
+    <t>Solicitante não informado</t>
+  </si>
+  <si>
+    <t>Equipe não informada</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>34335</t>
+  </si>
+  <si>
+    <t>Tempo Padrão - Homologação</t>
+  </si>
+  <si>
+    <t>Bom dia Srs., Favor criar uma aplicação que traga os tempos padrões cadastrados que estão sendo usados para cálculo do IROG. Trazer de todos os setores (Acabamento, Usinagem, Inspeção, Moldagem,...) Disponibilizar o ícone na aplicação IROG: Trazer as seguintes informações: * Modelo; * Operação; * Te</t>
+  </si>
+  <si>
+    <t>10/04/2026</t>
+  </si>
+  <si>
+    <t>Homologação</t>
+  </si>
+  <si>
+    <t>11134421691</t>
+  </si>
+  <si>
+    <t>Chamado para linkar o sistema Mess/ Manutenção - Reunião</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>29/01/2026</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>Janeiro</t>
+  </si>
+  <si>
+    <t>11340065850</t>
+  </si>
+  <si>
+    <t>Sistema de reconhecimento e conferência</t>
+  </si>
+  <si>
+    <t>36692</t>
+  </si>
+  <si>
+    <t>Logistica</t>
+  </si>
+  <si>
+    <t>Sequencias de conjunto</t>
+  </si>
+  <si>
+    <t>Boa tarde, Maciel. Conforme conversamos, precisamos que as informações das sequências do conjunto sejam exibidas diretamente na tela atual do WMS. Atualmente, a consulta dessas sequências precisa ser feita por meio de outras telas, o que tem aumentado nosso tempo de análise e, consequentemente, noss</t>
+  </si>
+  <si>
+    <t>Rodrigo Santos Rocha</t>
+  </si>
+  <si>
+    <t>Impedimento</t>
+  </si>
+  <si>
+    <t>11329687336</t>
+  </si>
+  <si>
+    <t>Divergência no Relatório Funil Vendas 80%</t>
+  </si>
+  <si>
+    <t>02/03/2026</t>
+  </si>
+  <si>
+    <t>35467</t>
+  </si>
+  <si>
+    <t>Controladoria</t>
+  </si>
+  <si>
+    <t>Alterar Cálculo do Custo de SUCATA RETORNO</t>
+  </si>
+  <si>
+    <t>Bom dia a todos! O processo de controle dos estoques de SUCATA RETORNO está em aprimoramento, para tanto, é preciso implementar alterações de sistema válidas a partir de 01/01/2026: Segue forma de cálculo: 1. Entrada em estoque a partir Corte de Canal. * Peso a ser considerado para Entrada, peso ali</t>
+  </si>
+  <si>
+    <t>Paulo Giovani da Cruz</t>
+  </si>
+  <si>
+    <t>11330415000</t>
+  </si>
+  <si>
+    <t>Add opção de revisão valor de frete na CPC</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>25173</t>
+  </si>
+  <si>
+    <t>Peças Faturadas</t>
+  </si>
+  <si>
+    <t>Boa tarde Srs., Preciso que seja desenvolvido no QlikSense uma tabela trazendo todos os modelos faturados por mês / ano e seus devidos valores cobrados (FTF) para ensaios de qualidade. Descrição (Códigos FTF): · Hidrostático (7242); · Dimensional Braço Faro (7250) · Fotogrametria (7268); · Dimension</t>
+  </si>
+  <si>
+    <t>28/03/2024</t>
+  </si>
+  <si>
+    <t>Março</t>
+  </si>
+  <si>
+    <t>11329745056</t>
+  </si>
+  <si>
+    <t>Acessos anônimos</t>
+  </si>
+  <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>11340068586</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Aprimoramento Ailton - Valorização de modelos</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Criar agendamento que dispare o envio do lote de produtos.</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>Fevereiro</t>
-  </si>
-  <si>
-    <t>28392</t>
-  </si>
-  <si>
-    <t>Setor não informado</t>
-  </si>
-  <si>
-    <t>Notas de consignado - Medição NIMBI</t>
-  </si>
-  <si>
-    <t>Bom dia, Conforme reunião dia 10/10 com o Sandro, queremos solicitar uma alteração no sistema de consignados da empresa. Sobre os contratos de consignado será gerado uma ordem de compra, e dentro dessas ordens terão medições para os consumos dos consignados. Para verificar que a OC é referente a con</t>
-  </si>
-  <si>
-    <t>Jessica Priscila Gonçalves</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>23/02/2026</t>
-  </si>
-  <si>
-    <t>24/03/2026</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>36632</t>
-  </si>
-  <si>
-    <t>Categoria não informada</t>
-  </si>
-  <si>
-    <t>Multiplos de Caixa de ferro</t>
-  </si>
-  <si>
-    <t>Solicitante não informado</t>
-  </si>
-  <si>
-    <t>Equipe não informada</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>34335</t>
-  </si>
-  <si>
-    <t>Tempo Padrão - Homologação</t>
-  </si>
-  <si>
-    <t>Bom dia Srs., Favor criar uma aplicação que traga os tempos padrões cadastrados que estão sendo usados para cálculo do IROG. Trazer de todos os setores (Acabamento, Usinagem, Inspeção, Moldagem,...) Disponibilizar o ícone na aplicação IROG: Trazer as seguintes informações: * Modelo; * Operação; * Te</t>
-  </si>
-  <si>
-    <t>10/04/2026</t>
-  </si>
-  <si>
-    <t>Homologação</t>
-  </si>
-  <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>36231</t>
-  </si>
-  <si>
-    <t>Chamado para linkar o sistema Mess/ Manutenção - Reunião</t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
-    <t>29/01/2026</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
-  </si>
-  <si>
-    <t>Janeiro</t>
-  </si>
-  <si>
-    <t>35602</t>
-  </si>
-  <si>
-    <t>Sistema de reconhecimento e conferência</t>
-  </si>
-  <si>
-    <t>36692</t>
-  </si>
-  <si>
-    <t>Sequencias de conjunto</t>
-  </si>
-  <si>
-    <t>Boa tarde, Maciel. Conforme conversamos, precisamos que as informações das sequências do conjunto sejam exibidas diretamente na tela atual do WMS. Atualmente, a consulta dessas sequências precisa ser feita por meio de outras telas, o que tem aumentado nosso tempo de análise e, consequentemente, noss</t>
-  </si>
-  <si>
-    <t>Rodrigo Santos Rocha</t>
-  </si>
-  <si>
-    <t>Impedimento</t>
-  </si>
-  <si>
-    <t>36453</t>
-  </si>
-  <si>
-    <t>Divergência no Relatório Funil Vendas 80%</t>
-  </si>
-  <si>
-    <t>35467</t>
-  </si>
-  <si>
-    <t>Alterar Cálculo do Custo de SUCATA RETORNO</t>
-  </si>
-  <si>
-    <t>Bom dia a todos! O processo de controle dos estoques de SUCATA RETORNO está em aprimoramento, para tanto, é preciso implementar alterações de sistema válidas a partir de 01/01/2026: Segue forma de cálculo: 1. Entrada em estoque a partir Corte de Canal. * Peso a ser considerado para Entrada, peso ali</t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
-    <t>36398</t>
-  </si>
-  <si>
-    <t>Add opção de revisão valor de frete na CPC</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>25173</t>
-  </si>
-  <si>
-    <t>Peças Faturadas</t>
-  </si>
-  <si>
-    <t>Boa tarde Srs., Preciso que seja desenvolvido no QlikSense uma tabela trazendo todos os modelos faturados por mês / ano e seus devidos valores cobrados (FTF) para ensaios de qualidade. Descrição (Códigos FTF): · Hidrostático (7242); · Dimensional Braço Faro (7250) · Fotogrametria (7268); · Dimension</t>
-  </si>
-  <si>
-    <t>28/03/2024</t>
-  </si>
-  <si>
-    <t>Março</t>
-  </si>
-  <si>
-    <t>36780</t>
-  </si>
-  <si>
-    <t>Acessos anônimos</t>
-  </si>
-  <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>36046</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Aprimoramento Ailton - Valorização de modelos</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Criar agendamento que dispare o envio do lote de produtos.</t>
-  </si>
-  <si>
     <t>Laura Herrmann Schmickler</t>
   </si>
   <si>
     <t>36320</t>
   </si>
   <si>
+    <t>Manutenção</t>
+  </si>
+  <si>
     <t>Linkar gatilho de ACR com TV manutenções (Central + Usinagem)</t>
   </si>
   <si>
@@ -339,18 +357,18 @@
     <t>25/02/2026</t>
   </si>
   <si>
-    <t>31977</t>
+    <t>11340066411</t>
   </si>
   <si>
     <t>Alterações no registro de moldagem via APP - Validação</t>
   </si>
   <si>
+    <t>01/03/2026</t>
+  </si>
+  <si>
     <t>36730</t>
   </si>
   <si>
-    <t>Manutenção</t>
-  </si>
-  <si>
     <t>Arvore de Ativos no sistema SMI</t>
   </si>
   <si>
@@ -363,7 +381,7 @@
     <t>18/03/2026</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>11340053791</t>
   </si>
   <si>
     <t>Novo Sistema</t>
@@ -396,7 +414,7 @@
     <t>Bom dia, Estamos solicitando que seja feito uma alteração no sistema de manutenção que envolve a seguinte mudança: Ordens preventivas e provenientes de métodos não devem ser programadas diretas, devem passar pela programação antes, ou seja, devem ser abertas com status de aguardando programação. Con</t>
   </si>
   <si>
-    <t>34073</t>
+    <t>11247252954</t>
   </si>
   <si>
     <t>ALTC - Adicionar botão para visualização da FTFU (CPP123,CPP39)</t>
@@ -408,6 +426,9 @@
     <t>36232</t>
   </si>
   <si>
+    <t>Mecânica</t>
+  </si>
+  <si>
     <t>Report técnico</t>
   </si>
   <si>
@@ -420,13 +441,13 @@
     <t>19/05/2026</t>
   </si>
   <si>
-    <t>36724</t>
+    <t>11326263820</t>
   </si>
   <si>
     <t>Alteração de registro de pintura</t>
   </si>
   <si>
-    <t>36526</t>
+    <t>11329309931</t>
   </si>
   <si>
     <t>Tempo de parada Carrossel</t>
@@ -447,7 +468,7 @@
     <t>22/04/2026</t>
   </si>
   <si>
-    <t>36493</t>
+    <t>11329443224</t>
   </si>
   <si>
     <t>Apontamento Eletrônico Acabamento - Analise</t>
@@ -456,12 +477,27 @@
     <t>36722</t>
   </si>
   <si>
+    <t>TI</t>
+  </si>
+  <si>
     <t>Bloco K - Integração dados Altona / Benner.</t>
   </si>
   <si>
+    <t>Prezado, bom dia. Situação: Atualmente a integração dos dados Altona / Benner, para integrar o bloco K, precisa da intervenção de uma pessoa para disparar a rotina. Necessidade: Automatizar este processo. Ação: 1. Implementar status indicando que o dado está pronto para ser enviado para Benner. 2. A</t>
+  </si>
+  <si>
+    <t>Alexandre Longo</t>
+  </si>
+  <si>
+    <t>11/06/2026</t>
+  </si>
+  <si>
     <t>35738</t>
   </si>
   <si>
+    <t>Fundição</t>
+  </si>
+  <si>
     <t>Melhoria apontamento de corte de canais - Reunião</t>
   </si>
   <si>
@@ -471,22 +507,25 @@
     <t>Eduardo Basso Pinto</t>
   </si>
   <si>
+    <t>11247261561</t>
+  </si>
+  <si>
     <t>ALTC - Adicionar consulta de ensaios realizados F9</t>
   </si>
   <si>
-    <t>35081</t>
+    <t>11340072612</t>
   </si>
   <si>
     <t>SUGESTÃO PARA MELHORIA NA H5000 - Reunião</t>
   </si>
   <si>
-    <t>31699</t>
+    <t>11340075494</t>
   </si>
   <si>
     <t>Cadastro de TOKEN Ailton</t>
   </si>
   <si>
-    <t>19909</t>
+    <t>11340072555</t>
   </si>
   <si>
     <t>Criar KB Genexus especifica para Registro de pinturas</t>
@@ -501,7 +540,7 @@
     <t>Sandro, bom dia! Solicito melhorias a seguir no Relatório Faturamento por Sequência. * Desconsiderar NF que não se tratam de venda (receita), por exemplo 210982/212675/213384/213385 (CFOP 5.949./6.949/7.949 - Remessa Conserto e Outros) NFe 213069 valor incorreto retornado no relatório.</t>
   </si>
   <si>
-    <t>36349</t>
+    <t>11330632238</t>
   </si>
   <si>
     <t>Erro ao excluir planos de ação - Gestão de ações</t>
@@ -519,7 +558,7 @@
     <t>Guilherme Ferreira</t>
   </si>
   <si>
-    <t>36210</t>
+    <t>11330756420</t>
   </si>
   <si>
     <t>[Residência em IA] Altona 1 - Envio de Resultados - Sprint 2</t>
@@ -540,6 +579,9 @@
     <t>36484</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Melhoria da Tela de Tickets</t>
   </si>
   <si>
@@ -564,7 +606,7 @@
     <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
   </si>
   <si>
-    <t>36778</t>
+    <t>11326628409</t>
   </si>
   <si>
     <t>Revogação de acessos - Troca de área</t>
@@ -576,7 +618,7 @@
     <t>Criar procedimento que envie lotes de Oportunidades</t>
   </si>
   <si>
-    <t>36407</t>
+    <t>11287715195</t>
   </si>
   <si>
     <t>Tela para programação de moldagem</t>
@@ -612,6 +654,12 @@
     <t>Incluir no cadastro de produtos a chamada do link (item 2.3)</t>
   </si>
   <si>
+    <t>26/02/2026</t>
+  </si>
+  <si>
+    <t>11366159340</t>
+  </si>
+  <si>
     <t>Publicar agendamento de entrega para acesso externo por fornecedor</t>
   </si>
   <si>
@@ -630,7 +678,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2026-08</t>
+    <t>Mar/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -682,6 +730,9 @@
   </si>
   <si>
     <t>Sim</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
   </si>
   <si>
     <t>Abertos</t>
@@ -1283,28 +1334,28 @@
         <v>39</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>36</v>
@@ -1313,7 +1364,7 @@
         <v>25</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>27</v>
@@ -1327,7 +1378,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1339,10 +1390,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>21</v>
@@ -1357,13 +1408,13 @@
         <v>24</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>28</v>
@@ -1377,13 +1428,13 @@
         <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>52</v>
@@ -1395,16 +1446,16 @@
         <v>53</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>54</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>26</v>
@@ -1424,13 +1475,13 @@
         <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>58</v>
@@ -1442,16 +1493,16 @@
         <v>53</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>36</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>26</v>
@@ -1471,7 +1522,7 @@
         <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>17</v>
@@ -1480,16 +1531,16 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>35</v>
@@ -1498,13 +1549,13 @@
         <v>24</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>28</v>
@@ -1515,37 +1566,37 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>26</v>
@@ -1562,10 +1613,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>17</v>
@@ -1574,16 +1625,16 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>35</v>
@@ -1592,7 +1643,7 @@
         <v>36</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>26</v>
@@ -1609,43 +1660,43 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>28</v>
@@ -1656,7 +1707,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1668,10 +1719,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>21</v>
@@ -1683,13 +1734,13 @@
         <v>23</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>37</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>27</v>
@@ -1698,48 +1749,48 @@
         <v>38</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>28</v>
@@ -1750,43 +1801,43 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>36</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>38</v>
@@ -1797,10 +1848,10 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>17</v>
@@ -1809,16 +1860,16 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>23</v>
@@ -1827,13 +1878,13 @@
         <v>36</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>38</v>
@@ -1844,10 +1895,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>17</v>
@@ -1856,16 +1907,16 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>23</v>
@@ -1874,13 +1925,13 @@
         <v>36</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>38</v>
@@ -1891,22 +1942,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>53</v>
@@ -1938,10 +1989,10 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>17</v>
@@ -1950,16 +2001,16 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>23</v>
@@ -1985,46 +2036,46 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>29</v>
@@ -2032,10 +2083,10 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>17</v>
@@ -2044,16 +2095,16 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>23</v>
@@ -2062,13 +2113,13 @@
         <v>36</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>38</v>
@@ -2079,22 +2130,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>21</v>
@@ -2106,7 +2157,7 @@
         <v>23</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>37</v>
@@ -2126,37 +2177,37 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>36</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>26</v>
@@ -2173,10 +2224,10 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>17</v>
@@ -2185,16 +2236,16 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>23</v>
@@ -2203,13 +2254,13 @@
         <v>24</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>28</v>
@@ -2220,43 +2271,43 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>36</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>38</v>
@@ -2267,10 +2318,10 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>17</v>
@@ -2279,16 +2330,16 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>23</v>
@@ -2300,10 +2351,10 @@
         <v>37</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>38</v>
@@ -2314,10 +2365,10 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>17</v>
@@ -2326,16 +2377,16 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>23</v>
@@ -2344,7 +2395,7 @@
         <v>36</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>26</v>
@@ -2361,10 +2412,10 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>17</v>
@@ -2373,16 +2424,16 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>23</v>
@@ -2391,7 +2442,7 @@
         <v>36</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>26</v>
@@ -2408,37 +2459,37 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>26</v>
@@ -2447,7 +2498,7 @@
         <v>27</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>29</v>
@@ -2455,10 +2506,10 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>17</v>
@@ -2467,16 +2518,16 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>23</v>
@@ -2485,7 +2536,7 @@
         <v>36</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>26</v>
@@ -2502,43 +2553,43 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>28</v>
@@ -2549,43 +2600,43 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>28</v>
@@ -2596,28 +2647,28 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>35</v>
@@ -2626,13 +2677,13 @@
         <v>36</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>38</v>
@@ -2643,37 +2694,37 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>26</v>
@@ -2690,43 +2741,43 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>42</v>
+        <v>157</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>25</v>
+        <v>158</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>28</v>
@@ -2737,10 +2788,10 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>31</v>
+        <v>160</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>17</v>
@@ -2749,16 +2800,16 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>23</v>
@@ -2767,7 +2818,7 @@
         <v>36</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>26</v>
@@ -2784,37 +2835,37 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>26</v>
@@ -2823,7 +2874,7 @@
         <v>27</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>29</v>
@@ -2831,43 +2882,43 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>36</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>38</v>
@@ -2878,37 +2929,37 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>36</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>26</v>
@@ -2925,43 +2976,43 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>36</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>38</v>
@@ -2972,10 +3023,10 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>17</v>
@@ -2984,16 +3035,16 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>23</v>
@@ -3002,7 +3053,7 @@
         <v>36</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>26</v>
@@ -3019,43 +3070,43 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>28</v>
@@ -3066,10 +3117,10 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>17</v>
@@ -3078,16 +3129,16 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>23</v>
@@ -3099,10 +3150,10 @@
         <v>37</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>28</v>
@@ -3113,43 +3164,43 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>28</v>
@@ -3160,28 +3211,28 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>23</v>
@@ -3190,13 +3241,13 @@
         <v>36</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>38</v>
@@ -3207,10 +3258,10 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>17</v>
@@ -3219,16 +3270,16 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>23</v>
@@ -3240,7 +3291,7 @@
         <v>37</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>27</v>
@@ -3254,28 +3305,28 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>23</v>
@@ -3287,10 +3338,10 @@
         <v>37</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>38</v>
@@ -3301,28 +3352,28 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>23</v>
@@ -3331,13 +3382,13 @@
         <v>36</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>38</v>
@@ -3348,43 +3399,43 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>28</v>
@@ -3395,10 +3446,10 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>17</v>
@@ -3407,16 +3458,16 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>23</v>
@@ -3425,7 +3476,7 @@
         <v>36</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>26</v>
@@ -3442,10 +3493,10 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>17</v>
@@ -3454,16 +3505,16 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>23</v>
@@ -3472,13 +3523,13 @@
         <v>36</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>38</v>
@@ -3489,40 +3540,40 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>27</v>
@@ -3536,28 +3587,28 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>23</v>
@@ -3566,13 +3617,13 @@
         <v>24</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>28</v>
@@ -3583,10 +3634,10 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>17</v>
@@ -3595,31 +3646,31 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>38</v>
@@ -3630,10 +3681,10 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>17</v>
@@ -3642,25 +3693,25 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>25</v>
+        <v>213</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>26</v>
@@ -3669,7 +3720,7 @@
         <v>27</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>29</v>
@@ -3677,43 +3728,43 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>116</v>
+        <v>214</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>25</v>
+        <v>211</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>38</v>
@@ -3724,10 +3775,10 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>17</v>
@@ -3736,16 +3787,16 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>23</v>
@@ -3754,7 +3805,7 @@
         <v>24</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>26</v>
@@ -3782,23 +3833,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="D2" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="E2" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3806,16 +3857,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3826,15 +3877,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>101.33</v>
+        <v>52.42</v>
       </c>
       <c r="J5" s="4">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3847,7 +3898,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K23">
         <v>4</v>
@@ -3855,7 +3906,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3886,12 +3937,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="B2">
         <v>55</v>
@@ -3905,43 +3956,43 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>101.33</v>
+        <v>52.42</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B10">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -3950,13 +4001,13 @@
         <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3968,21 +4019,21 @@
         <v>22</v>
       </c>
       <c r="P10" t="s">
-        <v>104</v>
+        <v>239</v>
       </c>
       <c r="Q10">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
         <v>85</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="D11" t="s">
-        <v>82</v>
       </c>
       <c r="E11">
         <v>7</v>
@@ -3997,19 +4048,19 @@
         <v>27</v>
       </c>
       <c r="K11">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="M11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="N11">
         <v>17</v>
       </c>
       <c r="P11" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -4017,10 +4068,10 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -4032,100 +4083,144 @@
         <v>31</v>
       </c>
       <c r="J12" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="K12">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N12">
         <v>3</v>
       </c>
       <c r="P12" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="Q12">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N13">
         <v>6</v>
       </c>
       <c r="P13" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Q13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
       <c r="G14" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N14">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="13:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
       <c r="M15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N15">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="13:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
       <c r="M16" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="N16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="13:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
       <c r="M17" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="N17">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>154</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>160</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
       <c r="D19" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>188</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -4133,7 +4228,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -4141,142 +4236,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>712</v>
+        <v>797</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="F22" s="2">
-        <v>71</v>
+        <v>797</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>131</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>159</v>
+        <v>73</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F23" s="2">
-        <v>44</v>
+        <v>797</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>160</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>200</v>
+        <v>81</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F24" s="2">
-        <v>35</v>
+        <v>797</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>201</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F25" s="2">
-        <v>32</v>
+        <v>797</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="F26" s="2">
-        <v>32</v>
+        <v>797</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>148</v>
+        <v>93</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="F27" s="2">
-        <v>32</v>
+        <v>797</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="F28" s="2">
-        <v>17</v>
+        <v>797</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="F29" s="2">
-        <v>17</v>
+        <v>797</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="F30" s="2">
-        <v>17</v>
+        <v>797</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>175</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
